--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,41 +587,47 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.0542</v>
+      </c>
+      <c r="E2">
+        <v>0.00414</v>
+      </c>
       <c r="G2">
-        <v>0.3013108980630014</v>
+        <v>0.3418562757000195</v>
       </c>
       <c r="H2">
-        <v>0.3013108980630014</v>
+        <v>0.3418836890542392</v>
       </c>
       <c r="I2">
-        <v>0.379182156133829</v>
+        <v>0.2567064813001762</v>
       </c>
       <c r="J2">
-        <v>0.3279783472992198</v>
+        <v>0.2276541712685403</v>
       </c>
       <c r="K2">
-        <v>258.8</v>
+        <v>231.7</v>
       </c>
       <c r="L2">
-        <v>0.5063588338876932</v>
+        <v>0.4536910123360094</v>
       </c>
       <c r="M2">
-        <v>369.9</v>
+        <v>176.8</v>
       </c>
       <c r="N2">
-        <v>0.06889294494524324</v>
+        <v>0.02458868197432652</v>
       </c>
       <c r="O2">
-        <v>1.429289026275116</v>
+        <v>0.7630556754423824</v>
       </c>
       <c r="P2">
-        <v>369.9</v>
+        <v>176.8</v>
       </c>
       <c r="Q2">
-        <v>0.06889294494524324</v>
+        <v>0.02458868197432652</v>
       </c>
       <c r="R2">
-        <v>1.429289026275116</v>
+        <v>0.7630556754423824</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -630,70 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>84.90000000000001</v>
+        <v>623.6900000000001</v>
       </c>
       <c r="V2">
-        <v>0.01581241153244431</v>
+        <v>0.08674046979959112</v>
       </c>
       <c r="W2">
-        <v>0.2115059221658206</v>
+        <v>0.1219818312632377</v>
       </c>
       <c r="X2">
-        <v>0.02567455775213807</v>
+        <v>0.05732232827595285</v>
       </c>
       <c r="Y2">
-        <v>0.1858313644136826</v>
+        <v>0.06465950298728487</v>
       </c>
       <c r="Z2">
-        <v>0.3616103014008773</v>
+        <v>0.1588867041664593</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.02629089632751664</v>
+        <v>0.05413693048199675</v>
       </c>
       <c r="AC2">
-        <v>-0.02629089632751664</v>
+        <v>-0.05413693048199675</v>
       </c>
       <c r="AD2">
-        <v>742.14</v>
+        <v>1343.237</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>742.14</v>
+        <v>1343.237</v>
       </c>
       <c r="AG2">
-        <v>657.24</v>
+        <v>719.5469999999998</v>
       </c>
       <c r="AH2">
-        <v>0.1214365425585878</v>
+        <v>0.1574068290791966</v>
       </c>
       <c r="AI2">
-        <v>0.3413801668859306</v>
+        <v>0.4099688167359848</v>
       </c>
       <c r="AJ2">
-        <v>0.1090594115265397</v>
+        <v>0.09096851051606938</v>
       </c>
       <c r="AK2">
-        <v>0.3146134109447402</v>
+        <v>0.2712459951891378</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.096</v>
       </c>
       <c r="AM2">
-        <v>-9.550000000000001</v>
+        <v>-13.904</v>
       </c>
       <c r="AN2">
-        <v>3.618430034129693</v>
+        <v>9.399839048285513</v>
+      </c>
+      <c r="AO2">
+        <v>1365.625</v>
       </c>
       <c r="AP2">
-        <v>3.204485616772306</v>
+        <v>5.035318404478655</v>
       </c>
       <c r="AQ2">
-        <v>-20.29319371727749</v>
+        <v>-9.428941311852704</v>
       </c>
     </row>
     <row r="3">
@@ -713,40 +722,40 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.4475443185120604</v>
+        <v>0.5926205023761031</v>
       </c>
       <c r="H3">
-        <v>0.4475443185120604</v>
+        <v>0.5926680244399185</v>
       </c>
       <c r="I3">
-        <v>0.5632083696599826</v>
+        <v>0.445010183299389</v>
       </c>
       <c r="J3">
-        <v>0.46346207327206</v>
+        <v>0.3898436316507043</v>
       </c>
       <c r="K3">
-        <v>168.2</v>
+        <v>127.2</v>
       </c>
       <c r="L3">
-        <v>0.4888113920371984</v>
+        <v>0.4317718940936863</v>
       </c>
       <c r="M3">
-        <v>298.6</v>
+        <v>95.8</v>
       </c>
       <c r="N3">
-        <v>0.07426198114849909</v>
+        <v>0.01657439446366782</v>
       </c>
       <c r="O3">
-        <v>1.775267538644471</v>
+        <v>0.7531446540880503</v>
       </c>
       <c r="P3">
-        <v>298.6</v>
+        <v>95.8</v>
       </c>
       <c r="Q3">
-        <v>0.07426198114849909</v>
+        <v>0.01657439446366782</v>
       </c>
       <c r="R3">
-        <v>1.775267538644471</v>
+        <v>0.7531446540880503</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -755,55 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>28.6</v>
+        <v>558.7</v>
       </c>
       <c r="V3">
-        <v>0.007112835434852894</v>
+        <v>0.09666089965397924</v>
+      </c>
+      <c r="W3">
+        <v>0.1594784353059178</v>
       </c>
       <c r="X3">
-        <v>0.02430494137648706</v>
+        <v>0.05005742440148585</v>
+      </c>
+      <c r="Y3">
+        <v>0.1094210109044319</v>
+      </c>
+      <c r="Z3">
+        <v>0.3824781886165352</v>
+      </c>
+      <c r="AA3">
+        <v>0.1491066860774531</v>
       </c>
       <c r="AB3">
-        <v>0.0243065733267408</v>
+        <v>0.05005756141599317</v>
+      </c>
+      <c r="AC3">
+        <v>0.09904912466145997</v>
       </c>
       <c r="AD3">
-        <v>1.24</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.24</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="AG3">
-        <v>-27.36</v>
+        <v>-557.763</v>
       </c>
       <c r="AH3">
-        <v>0.000308293594951941</v>
+        <v>0.0001620844510154669</v>
       </c>
       <c r="AI3">
-        <v>0.00155225076360723</v>
+        <v>0.001134331755115086</v>
       </c>
       <c r="AJ3">
-        <v>-0.006851064469117625</v>
+        <v>-0.1068053786145669</v>
       </c>
       <c r="AK3">
-        <v>-0.03552139592854175</v>
+        <v>-2.08636664584401</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.096</v>
       </c>
       <c r="AM3">
-        <v>-9.550000000000001</v>
+        <v>-13.904</v>
       </c>
       <c r="AN3">
-        <v>0.006045831301803998</v>
+        <v>0.00655703289013296</v>
+      </c>
+      <c r="AO3">
+        <v>1365.625</v>
       </c>
       <c r="AP3">
-        <v>-0.1333983422720624</v>
+        <v>-3.903170048985305</v>
       </c>
       <c r="AQ3">
-        <v>-20.29319371727749</v>
+        <v>-9.428941311852704</v>
       </c>
     </row>
     <row r="4">
@@ -835,28 +862,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>62.5</v>
+        <v>49.7</v>
       </c>
       <c r="L4">
-        <v>0.5852059925093633</v>
+        <v>0.5139607032057911</v>
       </c>
       <c r="M4">
-        <v>33.9</v>
+        <v>39.9</v>
       </c>
       <c r="N4">
-        <v>0.0404679479527277</v>
+        <v>0.07899425856266085</v>
       </c>
       <c r="O4">
-        <v>0.5424</v>
+        <v>0.8028169014084506</v>
       </c>
       <c r="P4">
-        <v>33.9</v>
+        <v>39.9</v>
       </c>
       <c r="Q4">
-        <v>0.0404679479527277</v>
+        <v>0.07899425856266085</v>
       </c>
       <c r="R4">
-        <v>0.5424</v>
+        <v>0.8028169014084506</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -865,55 +892,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>24.9</v>
+        <v>22.4</v>
       </c>
       <c r="V4">
-        <v>0.02972424495642831</v>
+        <v>0.04434765392991486</v>
       </c>
       <c r="W4">
-        <v>0.2115059221658206</v>
+        <v>0.1533477321814255</v>
       </c>
       <c r="X4">
-        <v>0.02567455775213807</v>
+        <v>0.05305101837612601</v>
       </c>
       <c r="Y4">
-        <v>0.1858313644136826</v>
+        <v>0.1002967138052995</v>
       </c>
       <c r="Z4">
-        <v>0.2318211417408292</v>
+        <v>0.212387436854821</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.02629089632751664</v>
+        <v>0.05097734625925174</v>
       </c>
       <c r="AC4">
-        <v>-0.02629089632751664</v>
+        <v>-0.05097734625925174</v>
       </c>
       <c r="AD4">
-        <v>156.1</v>
+        <v>168</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>156.1</v>
+        <v>168</v>
       </c>
       <c r="AG4">
-        <v>131.2</v>
+        <v>145.6</v>
       </c>
       <c r="AH4">
-        <v>0.1570738579190984</v>
+        <v>0.2495914425791116</v>
       </c>
       <c r="AI4">
-        <v>0.3250728862973761</v>
+        <v>0.3350618268847228</v>
       </c>
       <c r="AJ4">
-        <v>0.1354112911549179</v>
+        <v>0.2237590287382818</v>
       </c>
       <c r="AK4">
-        <v>0.2881616516582473</v>
+        <v>0.3039665970772443</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -930,111 +957,239 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Saudi Home Loans Company (SASE:1183)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.0579</v>
+      </c>
+      <c r="E5">
+        <v>0.008189999999999999</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>26.7</v>
+      </c>
+      <c r="L5">
+        <v>0.4548551959114139</v>
+      </c>
+      <c r="M5">
+        <v>20.6</v>
+      </c>
+      <c r="N5">
+        <v>0.03779816513761468</v>
+      </c>
+      <c r="O5">
+        <v>0.7715355805243447</v>
+      </c>
+      <c r="P5">
+        <v>20.6</v>
+      </c>
+      <c r="Q5">
+        <v>0.03779816513761468</v>
+      </c>
+      <c r="R5">
+        <v>0.7715355805243447</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>35.8</v>
+      </c>
+      <c r="V5">
+        <v>0.06568807339449541</v>
+      </c>
+      <c r="W5">
+        <v>0.05998651988317232</v>
+      </c>
+      <c r="X5">
+        <v>0.06159363817577968</v>
+      </c>
+      <c r="Y5">
+        <v>-0.001607118292607367</v>
+      </c>
+      <c r="Z5">
+        <v>0.05216850337717738</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.05729651470474176</v>
+      </c>
+      <c r="AC5">
+        <v>-0.05729651470474176</v>
+      </c>
+      <c r="AD5">
+        <v>698.3</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>698.3</v>
+      </c>
+      <c r="AG5">
+        <v>662.5</v>
+      </c>
+      <c r="AH5">
+        <v>0.5616504463926647</v>
+      </c>
+      <c r="AI5">
+        <v>0.607798764035164</v>
+      </c>
+      <c r="AJ5">
+        <v>0.5486542443064182</v>
+      </c>
+      <c r="AK5">
+        <v>0.5951846195310395</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Amlak International for Real Estate Finance Company (SASE:1182)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
+      <c r="D6">
+        <v>0.0505</v>
+      </c>
+      <c r="E6">
+        <v>8.999999999999999e-05</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
         <v>28.1</v>
       </c>
-      <c r="L5">
-        <v>0.4667774086378738</v>
-      </c>
-      <c r="M5">
-        <v>37.4</v>
-      </c>
-      <c r="N5">
-        <v>0.07324716020368194</v>
-      </c>
-      <c r="O5">
-        <v>1.330960854092527</v>
-      </c>
-      <c r="P5">
-        <v>37.4</v>
-      </c>
-      <c r="Q5">
-        <v>0.07324716020368194</v>
-      </c>
-      <c r="R5">
-        <v>1.330960854092527</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>31.4</v>
-      </c>
-      <c r="V5">
-        <v>0.06149627888758323</v>
-      </c>
-      <c r="W5">
-        <v>0.09366666666666668</v>
-      </c>
-      <c r="X5">
-        <v>0.0327346678234627</v>
-      </c>
-      <c r="Y5">
-        <v>0.06093199884320397</v>
-      </c>
-      <c r="Z5">
-        <v>0.06318883174136664</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.0310603307653329</v>
-      </c>
-      <c r="AC5">
-        <v>-0.0310603307653329</v>
-      </c>
-      <c r="AD5">
-        <v>584.8</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>584.8</v>
-      </c>
-      <c r="AG5">
-        <v>553.4</v>
-      </c>
-      <c r="AH5">
-        <v>0.533868906335585</v>
-      </c>
-      <c r="AI5">
-        <v>0.6534808358475807</v>
-      </c>
-      <c r="AJ5">
-        <v>0.5201127819548872</v>
-      </c>
-      <c r="AK5">
-        <v>0.640880138969311</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
+      <c r="L6">
+        <v>0.4629324546952224</v>
+      </c>
+      <c r="M6">
+        <v>20.5</v>
+      </c>
+      <c r="N6">
+        <v>0.05691282620766241</v>
+      </c>
+      <c r="O6">
+        <v>0.7295373665480427</v>
+      </c>
+      <c r="P6">
+        <v>20.5</v>
+      </c>
+      <c r="Q6">
+        <v>0.05691282620766241</v>
+      </c>
+      <c r="R6">
+        <v>0.7295373665480427</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>6.79</v>
+      </c>
+      <c r="V6">
+        <v>0.0188506385341477</v>
+      </c>
+      <c r="W6">
+        <v>0.09061593034504999</v>
+      </c>
+      <c r="X6">
+        <v>0.06195566294244446</v>
+      </c>
+      <c r="Y6">
+        <v>0.02866026740260552</v>
+      </c>
+      <c r="Z6">
+        <v>0.07029530978575566</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.05739437919590005</v>
+      </c>
+      <c r="AC6">
+        <v>-0.05739437919590005</v>
+      </c>
+      <c r="AD6">
+        <v>476</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>476</v>
+      </c>
+      <c r="AG6">
+        <v>469.21</v>
+      </c>
+      <c r="AH6">
+        <v>0.5692418081798613</v>
+      </c>
+      <c r="AI6">
+        <v>0.594925634295713</v>
+      </c>
+      <c r="AJ6">
+        <v>0.5657153880469249</v>
+      </c>
+      <c r="AK6">
+        <v>0.5914585723109503</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0542</v>
+        <v>-0.0164</v>
       </c>
       <c r="E2">
-        <v>0.00414</v>
+        <v>-0.176</v>
       </c>
       <c r="G2">
-        <v>0.3418562757000195</v>
+        <v>0.2233380681818182</v>
       </c>
       <c r="H2">
-        <v>0.3418836890542392</v>
+        <v>0.2166193181818182</v>
       </c>
       <c r="I2">
-        <v>0.2567064813001762</v>
+        <v>0.1132429290893878</v>
       </c>
       <c r="J2">
-        <v>0.2276541712685403</v>
+        <v>0.1015028955630811</v>
       </c>
       <c r="K2">
-        <v>231.7</v>
+        <v>146.98</v>
       </c>
       <c r="L2">
-        <v>0.4536910123360094</v>
+        <v>0.2087784090909091</v>
       </c>
       <c r="M2">
-        <v>176.8</v>
+        <v>125.62</v>
       </c>
       <c r="N2">
-        <v>0.02458868197432652</v>
+        <v>0.0155917982325489</v>
       </c>
       <c r="O2">
-        <v>0.7630556754423824</v>
+        <v>0.8546741053204518</v>
       </c>
       <c r="P2">
-        <v>176.8</v>
+        <v>125.62</v>
       </c>
       <c r="Q2">
-        <v>0.02458868197432652</v>
+        <v>0.0155917982325489</v>
       </c>
       <c r="R2">
-        <v>0.7630556754423824</v>
+        <v>0.8546741053204518</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>623.6900000000001</v>
+        <v>649.3200000000001</v>
       </c>
       <c r="V2">
-        <v>0.08674046979959112</v>
+        <v>0.08059279118260351</v>
       </c>
       <c r="W2">
-        <v>0.1219818312632377</v>
+        <v>0.06277472527472529</v>
       </c>
       <c r="X2">
-        <v>0.05732232827595285</v>
+        <v>0.0590261629287015</v>
       </c>
       <c r="Y2">
-        <v>0.06465950298728487</v>
+        <v>0.003748562346023783</v>
       </c>
       <c r="Z2">
-        <v>0.1588867041664593</v>
+        <v>0.2039892715900683</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05413693048199675</v>
+        <v>0.05260059801173791</v>
       </c>
       <c r="AC2">
-        <v>-0.05413693048199675</v>
+        <v>-0.05272587433487601</v>
       </c>
       <c r="AD2">
-        <v>1343.237</v>
+        <v>1945.4</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.234889605355057</v>
       </c>
       <c r="AF2">
-        <v>1343.237</v>
+        <v>1946.634889605355</v>
       </c>
       <c r="AG2">
-        <v>719.5469999999998</v>
+        <v>1297.314889605355</v>
       </c>
       <c r="AH2">
-        <v>0.1574068290791966</v>
+        <v>0.1945966471604786</v>
       </c>
       <c r="AI2">
-        <v>0.4099688167359848</v>
+        <v>0.4404714490044642</v>
       </c>
       <c r="AJ2">
-        <v>0.09096851051606938</v>
+        <v>0.1386892191207722</v>
       </c>
       <c r="AK2">
-        <v>0.2712459951891378</v>
+        <v>0.3441048688415843</v>
       </c>
       <c r="AL2">
-        <v>0.096</v>
+        <v>21.266</v>
       </c>
       <c r="AM2">
-        <v>-13.904</v>
+        <v>-27.034</v>
       </c>
       <c r="AN2">
-        <v>9.399839048285513</v>
+        <v>20.22245322245322</v>
       </c>
       <c r="AO2">
-        <v>1365.625</v>
+        <v>3.6993322674692</v>
       </c>
       <c r="AP2">
-        <v>5.035318404478655</v>
+        <v>13.48560176304943</v>
       </c>
       <c r="AQ2">
-        <v>-9.428941311852704</v>
+        <v>-2.91003920988385</v>
       </c>
     </row>
     <row r="3">
@@ -722,40 +722,40 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.5926205023761031</v>
+        <v>0.4749902610050643</v>
       </c>
       <c r="H3">
-        <v>0.5926680244399185</v>
+        <v>0.4565640825866771</v>
       </c>
       <c r="I3">
-        <v>0.445010183299389</v>
+        <v>0.2610050642773666</v>
       </c>
       <c r="J3">
-        <v>0.3898436316507043</v>
+        <v>0.2245306723547582</v>
       </c>
       <c r="K3">
-        <v>127.2</v>
+        <v>94.8</v>
       </c>
       <c r="L3">
-        <v>0.4317718940936863</v>
+        <v>0.3693026879626022</v>
       </c>
       <c r="M3">
-        <v>95.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="N3">
-        <v>0.01657439446366782</v>
+        <v>0.0120405370177268</v>
       </c>
       <c r="O3">
-        <v>0.7531446540880503</v>
+        <v>0.779535864978903</v>
       </c>
       <c r="P3">
-        <v>95.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="Q3">
-        <v>0.01657439446366782</v>
+        <v>0.0120405370177268</v>
       </c>
       <c r="R3">
-        <v>0.7531446540880503</v>
+        <v>0.779535864978903</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>558.7</v>
+        <v>523</v>
       </c>
       <c r="V3">
-        <v>0.09666089965397924</v>
+        <v>0.08521246089676746</v>
       </c>
       <c r="W3">
-        <v>0.1594784353059178</v>
+        <v>0.1148951642225185</v>
       </c>
       <c r="X3">
-        <v>0.05005742440148585</v>
+        <v>0.05237042742117143</v>
       </c>
       <c r="Y3">
-        <v>0.1094210109044319</v>
+        <v>0.06252473680134704</v>
       </c>
       <c r="Z3">
-        <v>0.3824781886165352</v>
+        <v>0.9602112689227454</v>
       </c>
       <c r="AA3">
-        <v>0.1491066860774531</v>
+        <v>0.2155968818138396</v>
       </c>
       <c r="AB3">
-        <v>0.05005756141599317</v>
+        <v>0.05232805723067772</v>
       </c>
       <c r="AC3">
-        <v>0.09904912466145997</v>
+        <v>0.1632688245831619</v>
       </c>
       <c r="AD3">
-        <v>0.9370000000000001</v>
+        <v>47.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.9370000000000001</v>
+        <v>47.3</v>
       </c>
       <c r="AG3">
-        <v>-557.763</v>
+        <v>-475.7</v>
       </c>
       <c r="AH3">
-        <v>0.0001620844510154669</v>
+        <v>0.00764765800578829</v>
       </c>
       <c r="AI3">
-        <v>0.001134331755115086</v>
+        <v>0.05442411690254286</v>
       </c>
       <c r="AJ3">
-        <v>-0.1068053786145669</v>
+        <v>-0.0840177325632738</v>
       </c>
       <c r="AK3">
-        <v>-2.08636664584401</v>
+        <v>-1.374458249060965</v>
       </c>
       <c r="AL3">
-        <v>0.096</v>
+        <v>0.026</v>
       </c>
       <c r="AM3">
-        <v>-13.904</v>
+        <v>-48.27399999999999</v>
       </c>
       <c r="AN3">
-        <v>0.00655703289013296</v>
+        <v>0.7188449848024316</v>
       </c>
       <c r="AO3">
-        <v>1365.625</v>
+        <v>2576.923076923077</v>
       </c>
       <c r="AP3">
-        <v>-3.903170048985305</v>
+        <v>-7.229483282674773</v>
       </c>
       <c r="AQ3">
-        <v>-9.428941311852704</v>
+        <v>-1.387910676554667</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Nayifat Finance Company (SASE:4081)</t>
+          <t>Taleem REIT Fund (SASE:4333)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,40 +850,40 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.9117647058823529</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.9117647058823529</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.8470588235294118</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.7795841478585392</v>
       </c>
       <c r="K4">
-        <v>49.7</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="L4">
-        <v>0.5139607032057911</v>
+        <v>0.5376470588235295</v>
       </c>
       <c r="M4">
-        <v>39.9</v>
+        <v>9.25</v>
       </c>
       <c r="N4">
-        <v>0.07899425856266085</v>
+        <v>0.06006493506493506</v>
       </c>
       <c r="O4">
-        <v>0.8028169014084506</v>
+        <v>1.012035010940919</v>
       </c>
       <c r="P4">
-        <v>39.9</v>
+        <v>9.25</v>
       </c>
       <c r="Q4">
-        <v>0.07899425856266085</v>
+        <v>0.06006493506493506</v>
       </c>
       <c r="R4">
-        <v>0.8028169014084506</v>
+        <v>1.012035010940919</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -892,61 +892,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>22.4</v>
+        <v>4.68</v>
       </c>
       <c r="V4">
-        <v>0.04434765392991486</v>
+        <v>0.03038961038961039</v>
       </c>
       <c r="W4">
-        <v>0.1533477321814255</v>
+        <v>0.06277472527472529</v>
       </c>
       <c r="X4">
-        <v>0.05305101837612601</v>
+        <v>0.0578573439154528</v>
       </c>
       <c r="Y4">
-        <v>0.1002967138052995</v>
+        <v>0.004917381359272492</v>
       </c>
       <c r="Z4">
-        <v>0.212387436854821</v>
+        <v>0.07774627275221807</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>0.06060976179271549</v>
       </c>
       <c r="AB4">
-        <v>0.05097734625925174</v>
+        <v>0.05251984683332236</v>
       </c>
       <c r="AC4">
-        <v>-0.05097734625925174</v>
+        <v>0.008089914959393124</v>
       </c>
       <c r="AD4">
-        <v>168</v>
+        <v>79.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>168</v>
+        <v>79.5</v>
       </c>
       <c r="AG4">
-        <v>145.6</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="AH4">
-        <v>0.2495914425791116</v>
+        <v>0.3404710920770878</v>
       </c>
       <c r="AI4">
-        <v>0.3350618268847228</v>
+        <v>0.3531763660595291</v>
       </c>
       <c r="AJ4">
-        <v>0.2237590287382818</v>
+        <v>0.3269819071759462</v>
       </c>
       <c r="AK4">
-        <v>0.3039665970772443</v>
+        <v>0.3394428817711641</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>4.84</v>
+      </c>
+      <c r="AN4">
+        <v>4.96875</v>
+      </c>
+      <c r="AO4">
+        <v>2.975206611570248</v>
+      </c>
+      <c r="AP4">
+        <v>4.67625</v>
+      </c>
+      <c r="AQ4">
+        <v>2.975206611570248</v>
       </c>
     </row>
     <row r="5">
@@ -957,7 +969,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Saudi Home Loans Company (SASE:1183)</t>
+          <t>Nayifat Finance Company (SASE:4081)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -965,12 +977,6 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.0579</v>
-      </c>
-      <c r="E5">
-        <v>0.008189999999999999</v>
-      </c>
       <c r="G5">
         <v>0</v>
       </c>
@@ -978,97 +984,100 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>0.01383734663507212</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>0.01183907098865435</v>
       </c>
       <c r="K5">
-        <v>26.7</v>
+        <v>29.1</v>
       </c>
       <c r="L5">
-        <v>0.4548551959114139</v>
+        <v>0.3823915900131407</v>
       </c>
       <c r="M5">
-        <v>20.6</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.03779816513761468</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.7715355805243447</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>20.6</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.03779816513761468</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.7715355805243447</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>35.8</v>
+        <v>13.7</v>
       </c>
       <c r="V5">
-        <v>0.06568807339449541</v>
+        <v>0.02912414965986395</v>
       </c>
       <c r="W5">
-        <v>0.05998651988317232</v>
+        <v>0.08728254349130175</v>
       </c>
       <c r="X5">
-        <v>0.06159363817577968</v>
+        <v>0.05623103838302805</v>
       </c>
       <c r="Y5">
-        <v>-0.001607118292607367</v>
+        <v>0.0310515051082737</v>
       </c>
       <c r="Z5">
-        <v>0.05216850337717738</v>
+        <v>0.158464121718722</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>0.001876067986182714</v>
       </c>
       <c r="AB5">
-        <v>0.05729651470474176</v>
+        <v>0.05247011836056738</v>
       </c>
       <c r="AC5">
-        <v>-0.05729651470474176</v>
+        <v>-0.05059405037438466</v>
       </c>
       <c r="AD5">
-        <v>698.3</v>
+        <v>170.7</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.234889605355057</v>
       </c>
       <c r="AF5">
-        <v>698.3</v>
+        <v>171.934889605355</v>
       </c>
       <c r="AG5">
-        <v>662.5</v>
+        <v>158.2348896053551</v>
       </c>
       <c r="AH5">
-        <v>0.5616504463926647</v>
+        <v>0.2676717276107956</v>
       </c>
       <c r="AI5">
-        <v>0.607798764035164</v>
+        <v>0.3214127418987364</v>
       </c>
       <c r="AJ5">
-        <v>0.5486542443064182</v>
+        <v>0.251711911352378</v>
       </c>
       <c r="AK5">
-        <v>0.5951846195310395</v>
+        <v>0.3035769338563659</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>131.3076923076923</v>
+      </c>
+      <c r="AP5">
+        <v>121.7191458502731</v>
       </c>
     </row>
     <row r="6">
@@ -1079,7 +1088,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amlak International for Real Estate Finance Company (SASE:1182)</t>
+          <t>Amlak International Finance Co (SASE:1182)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1088,10 +1097,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0505</v>
+        <v>-0.0164</v>
       </c>
       <c r="E6">
-        <v>8.999999999999999e-05</v>
+        <v>-0.162</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1106,28 +1115,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>28.1</v>
+        <v>10.4</v>
       </c>
       <c r="L6">
-        <v>0.4629324546952224</v>
+        <v>0.2374429223744292</v>
       </c>
       <c r="M6">
-        <v>20.5</v>
+        <v>19.3</v>
       </c>
       <c r="N6">
-        <v>0.05691282620766241</v>
+        <v>0.05848484848484849</v>
       </c>
       <c r="O6">
-        <v>0.7295373665480427</v>
+        <v>1.855769230769231</v>
       </c>
       <c r="P6">
-        <v>20.5</v>
+        <v>19.3</v>
       </c>
       <c r="Q6">
-        <v>0.05691282620766241</v>
+        <v>0.05848484848484849</v>
       </c>
       <c r="R6">
-        <v>0.7295373665480427</v>
+        <v>1.855769230769231</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1136,61 +1145,427 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>6.79</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="V6">
-        <v>0.0188506385341477</v>
+        <v>0.02890909090909091</v>
       </c>
       <c r="W6">
-        <v>0.09061593034504999</v>
+        <v>0.03208886146251157</v>
       </c>
       <c r="X6">
-        <v>0.06195566294244446</v>
+        <v>0.07164355728958489</v>
       </c>
       <c r="Y6">
-        <v>0.02866026740260552</v>
+        <v>-0.03955469582707333</v>
       </c>
       <c r="Z6">
-        <v>0.07029530978575566</v>
+        <v>0.05521170790737542</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05739437919590005</v>
+        <v>0.05272587433487601</v>
       </c>
       <c r="AC6">
-        <v>-0.05739437919590005</v>
+        <v>-0.05272587433487601</v>
       </c>
       <c r="AD6">
-        <v>476</v>
+        <v>592</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>476</v>
+        <v>592</v>
       </c>
       <c r="AG6">
-        <v>469.21</v>
+        <v>582.46</v>
       </c>
       <c r="AH6">
-        <v>0.5692418081798613</v>
+        <v>0.6420824295010846</v>
       </c>
       <c r="AI6">
-        <v>0.594925634295713</v>
+        <v>0.6514084507042254</v>
       </c>
       <c r="AJ6">
-        <v>0.5657153880469249</v>
+        <v>0.638340310808145</v>
       </c>
       <c r="AK6">
-        <v>0.5914585723109503</v>
+        <v>0.6477103396125704</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
         <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Morabaha Marina Financing Company (SASE:4082)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>12.8</v>
+      </c>
+      <c r="L7">
+        <v>0.2655601659751037</v>
+      </c>
+      <c r="M7">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="N7">
+        <v>0.0434419014084507</v>
+      </c>
+      <c r="O7">
+        <v>0.7710937499999999</v>
+      </c>
+      <c r="P7">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="Q7">
+        <v>0.0434419014084507</v>
+      </c>
+      <c r="R7">
+        <v>0.7710937499999999</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>52.2</v>
+      </c>
+      <c r="V7">
+        <v>0.2297535211267606</v>
+      </c>
+      <c r="W7">
+        <v>0.0877914951989026</v>
+      </c>
+      <c r="X7">
+        <v>0.0590261629287015</v>
+      </c>
+      <c r="Y7">
+        <v>0.0287653322702011</v>
+      </c>
+      <c r="Z7">
+        <v>0.1672333634029561</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.05515829470309272</v>
+      </c>
+      <c r="AC7">
+        <v>-0.05515829470309272</v>
+      </c>
+      <c r="AD7">
+        <v>141.9</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>141.9</v>
+      </c>
+      <c r="AG7">
+        <v>89.7</v>
+      </c>
+      <c r="AH7">
+        <v>0.3844486589000271</v>
+      </c>
+      <c r="AI7">
+        <v>0.3857026365860288</v>
+      </c>
+      <c r="AJ7">
+        <v>0.2830545913537394</v>
+      </c>
+      <c r="AK7">
+        <v>0.2841305036426988</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SHL Finance Company (SASE:1183)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>-0.00685</v>
+      </c>
+      <c r="E8">
+        <v>-0.19</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>6.84</v>
+      </c>
+      <c r="L8">
+        <v>0.178125</v>
+      </c>
+      <c r="M8">
+        <v>13.3</v>
+      </c>
+      <c r="N8">
+        <v>0.02725409836065574</v>
+      </c>
+      <c r="O8">
+        <v>1.944444444444445</v>
+      </c>
+      <c r="P8">
+        <v>13.3</v>
+      </c>
+      <c r="Q8">
+        <v>0.02725409836065574</v>
+      </c>
+      <c r="R8">
+        <v>1.944444444444445</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>34.9</v>
+      </c>
+      <c r="V8">
+        <v>0.07151639344262295</v>
+      </c>
+      <c r="W8">
+        <v>0.0151797603195739</v>
+      </c>
+      <c r="X8">
+        <v>0.0678197507753051</v>
+      </c>
+      <c r="Y8">
+        <v>-0.05263999045573119</v>
+      </c>
+      <c r="Z8">
+        <v>0.03449824813583684</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.05669398803505708</v>
+      </c>
+      <c r="AC8">
+        <v>-0.05669398803505708</v>
+      </c>
+      <c r="AD8">
+        <v>702.5</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>702.5</v>
+      </c>
+      <c r="AG8">
+        <v>667.6</v>
+      </c>
+      <c r="AH8">
+        <v>0.5900881982360353</v>
+      </c>
+      <c r="AI8">
+        <v>0.612307155931317</v>
+      </c>
+      <c r="AJ8">
+        <v>0.5777085496711666</v>
+      </c>
+      <c r="AK8">
+        <v>0.6001438331535419</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Saudi Printing and Packaging Co. (SASE:4270)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>-0.0305</v>
+      </c>
+      <c r="G9">
+        <v>0.08847184986595175</v>
+      </c>
+      <c r="H9">
+        <v>0.08847184986595175</v>
+      </c>
+      <c r="I9">
+        <v>-0.01219839142091153</v>
+      </c>
+      <c r="J9">
+        <v>-0.01219839142091153</v>
+      </c>
+      <c r="K9">
+        <v>-16.1</v>
+      </c>
+      <c r="L9">
+        <v>-0.07193923145665773</v>
+      </c>
+      <c r="M9">
+        <v>-0</v>
+      </c>
+      <c r="N9">
+        <v>-0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>-0</v>
+      </c>
+      <c r="Q9">
+        <v>-0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>11.3</v>
+      </c>
+      <c r="V9">
+        <v>0.0452724358974359</v>
+      </c>
+      <c r="W9">
+        <v>-0.09515366430260049</v>
+      </c>
+      <c r="X9">
+        <v>0.0614300906320685</v>
+      </c>
+      <c r="Y9">
+        <v>-0.156583754934669</v>
+      </c>
+      <c r="Z9">
+        <v>0.7709266276265931</v>
+      </c>
+      <c r="AA9">
+        <v>-0.00940406476059249</v>
+      </c>
+      <c r="AB9">
+        <v>0.05260059801173791</v>
+      </c>
+      <c r="AC9">
+        <v>-0.0620046627723304</v>
+      </c>
+      <c r="AD9">
+        <v>211.5</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>211.5</v>
+      </c>
+      <c r="AG9">
+        <v>200.2</v>
+      </c>
+      <c r="AH9">
+        <v>0.4586857514638907</v>
+      </c>
+      <c r="AI9">
+        <v>0.5773955773955773</v>
+      </c>
+      <c r="AJ9">
+        <v>0.4450867052023121</v>
+      </c>
+      <c r="AK9">
+        <v>0.563943661971831</v>
+      </c>
+      <c r="AL9">
+        <v>16.4</v>
+      </c>
+      <c r="AM9">
+        <v>16.4</v>
+      </c>
+      <c r="AN9">
+        <v>16.14503816793893</v>
+      </c>
+      <c r="AO9">
+        <v>-0.1664634146341464</v>
+      </c>
+      <c r="AP9">
+        <v>15.2824427480916</v>
+      </c>
+      <c r="AQ9">
+        <v>-0.1664634146341464</v>
       </c>
     </row>
   </sheetData>
